--- a/reports/2026-10-27_report.xlsx
+++ b/reports/2026-10-27_report.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 10:21 CAT</t>
+          <t>2026-10-27 11:58 CAT</t>
         </is>
       </c>
     </row>
